--- a/data/list_of_banks_ref_new.xlsx
+++ b/data/list_of_banks_ref_new.xlsx
@@ -6,7 +6,6 @@
     <sheet state="visible" name="Links" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Banks" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Email" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="link_type" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="201">
   <si>
     <t>bank</t>
   </si>
@@ -200,19 +199,13 @@
     <t>BankB</t>
   </si>
   <si>
-    <t>all_saving_accounts</t>
-  </si>
-  <si>
-    <t>Most info is in pdfs</t>
-  </si>
-  <si>
-    <t>https://www.bankb.be/fr-be/epargner</t>
-  </si>
-  <si>
     <t>https://www.bankb.be/fr-be/epargner/compte-depargne</t>
   </si>
   <si>
     <t>https://www.bankb.be/sites/default/files/documents/2025-03/Informations%20_cles_pour_l%27epargnant.pdf</t>
+  </si>
+  <si>
+    <t>https://www.bankb.be/fr-be/epargner/compte-terme</t>
   </si>
   <si>
     <t>Only useable info is in pdf.</t>
@@ -236,12 +229,6 @@
     <t>https://www.triodos.be/fr/actualite</t>
   </si>
   <si>
-    <t>few facts, but has links to other pages.</t>
-  </si>
-  <si>
-    <t>https://www.triodos.be/fr/epargner</t>
-  </si>
-  <si>
     <t>has everything, very nice</t>
   </si>
   <si>
@@ -257,25 +244,22 @@
     <t>https://www.triodos.be/fr/epargner/protocole-transparence-epargne</t>
   </si>
   <si>
-    <t>each product page is helpful: has figures conditions, etc...</t>
+    <t>https://www.triodos.be/fr/downloads/informations-cles-pour-lepargnant-triodos-impact-savings?id=31ff894e2429</t>
   </si>
   <si>
     <t>https://www.triodos.be/fr/epargner/compte-epargne</t>
   </si>
   <si>
+    <t>https://www.triodos.be/fr/downloads/informations-cles-pour-lepargnant-triodos-impact-savings-fidelity?id=1b64c09f7400</t>
+  </si>
+  <si>
     <t>https://www.triodos.be/fr/epargner/compte-epargne-fidelity</t>
   </si>
   <si>
-    <t>https://www.triodos.be/fr/epargner/compte-epargne-junior</t>
+    <t>https://www.triodos.be/fr/downloads/informations-cles-pour-lepargnant-triodos-impact-savings-junior?id=42ca350f1905</t>
   </si>
   <si>
-    <t>https://www.triodos.be/fr/downloads/informations-cles-pour-lepargnant-triodos-impact-savings?id=31ff894e2429</t>
-  </si>
-  <si>
-    <t>https://www.triodos.be/fr/downloads/informations-cles-pour-lepargnant-triodos-impact-savings-fidelity?id=1b64c09f7400</t>
-  </si>
-  <si>
-    <t>https://www.triodos.be/fr/downloads/informations-cles-pour-lepargnant-triodos-impact-savings-junior?id=42ca350f1905</t>
+    <t>https://www.triodos.be/fr/epargner/compte-epargne-junior</t>
   </si>
   <si>
     <t xml:space="preserve">Junior and adult are seperated. </t>
@@ -293,13 +277,10 @@
     <t>https://www.belfius.be/site/retail/fr/produits/epargner/comptes-epargne-reglementes</t>
   </si>
   <si>
-    <t>Beobank</t>
+    <t>Crelan</t>
   </si>
   <si>
     <t>https://www.crelan.be/fr/particuliers/epargner-et-investir/epargner/produit/comptes-terme</t>
-  </si>
-  <si>
-    <t>Crelan</t>
   </si>
   <si>
     <t>https://www.crelan.be/fr/particuliers/epargner-et-investir/epargner/produit/le-compte-depargne</t>
@@ -362,10 +343,64 @@
     <t>https://www.revolut.com/en-BE/our-pricing-plans/</t>
   </si>
   <si>
+    <t>Beobank</t>
+  </si>
+  <si>
+    <t>https://www.beobank.be/fr/epargner/comptes-epargne/compte-a-terme.html</t>
+  </si>
+  <si>
+    <t>https://www.beobank.be/fr/epargner/comptes-epargne/compte-save-plus.html</t>
+  </si>
+  <si>
+    <t>https://www.beobank.be/fr/epargner/comptes-epargne/compte-fidelity-plus.html</t>
+  </si>
+  <si>
+    <t>https://www.beobank.be/fr/epargner/comptes-epargne/compte-classique.html</t>
+  </si>
+  <si>
+    <t>Fintro</t>
+  </si>
+  <si>
+    <t>https://www.fintro.be/fr/public/particuliers/epargner-et-placer/epargner/comptes-epargne/comparatif</t>
+  </si>
+  <si>
+    <t>Keytrade</t>
+  </si>
+  <si>
+    <t>https://www.keytradebank.be/en/banking/savings</t>
+  </si>
+  <si>
+    <t>https://www.keytradebank.be/en/our-blog</t>
+  </si>
+  <si>
+    <t>https://www.keytradebank.be/en/banking/term-deposit-account</t>
+  </si>
+  <si>
+    <t>Santander</t>
+  </si>
+  <si>
+    <t>https://www.santanderconsumerbank.be/fr/comptes-depargne-reglementes</t>
+  </si>
+  <si>
+    <t>https://www.santanderconsumerbank.be/fr/epargner/comptes-terme/vision-fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santander </t>
+  </si>
+  <si>
+    <t>https://www.santanderconsumerbank.be/fr/epargner/comptes-terme/vision-green</t>
+  </si>
+  <si>
+    <t>https://www.santanderconsumerbank.be/fr/blog</t>
+  </si>
+  <si>
     <t>holding_group</t>
   </si>
   <si>
     <t>website</t>
+  </si>
+  <si>
+    <t>The program ignores this entire sheet. It is meant as a user reference.</t>
   </si>
   <si>
     <t>Argenta Group / Argenta Bank- en Verzekeringsgroep</t>
@@ -374,16 +409,10 @@
     <t>https://www.argenta.be</t>
   </si>
   <si>
-    <t>no overarching page found</t>
-  </si>
-  <si>
     <t>BNP Paribas Group</t>
   </si>
   <si>
     <t>https://www.bnpparibasfortis.be</t>
-  </si>
-  <si>
-    <t>not allowed to scrape</t>
   </si>
   <si>
     <t>Datex NV</t>
@@ -396,9 +425,6 @@
   </si>
   <si>
     <t>https://www.cph.be</t>
-  </si>
-  <si>
-    <t>Has all the info</t>
   </si>
   <si>
     <t>Triodos Bank N.V.</t>
@@ -447,9 +473,6 @@
   </si>
   <si>
     <t>https://www.europabank.be</t>
-  </si>
-  <si>
-    <t>Fintro</t>
   </si>
   <si>
     <t>BNP Paribas Fortis / BNP Paribas Group</t>
@@ -602,23 +625,38 @@
     <t>email</t>
   </si>
   <si>
-    <t>jan</t>
+    <t>Tien</t>
   </si>
   <si>
-    <t>Kazimirowski</t>
+    <t>BeCode</t>
   </si>
   <si>
-    <t>becode</t>
+    <t>hoanghanhtien97@gmail.com</t>
+  </si>
+  <si>
+    <t>Jan</t>
   </si>
   <si>
     <t>jan.kazimirowski@gmail.com</t>
+  </si>
+  <si>
+    <t>Kliti</t>
+  </si>
+  <si>
+    <t>hamatajkliti@gmail.com</t>
+  </si>
+  <si>
+    <t>Fernand</t>
+  </si>
+  <si>
+    <t>gaterafernand@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -663,6 +701,27 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -696,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -721,23 +780,50 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,10 +842,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1078,10 +1160,10 @@
       <c r="D3" s="7">
         <v>1.0</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -1120,8 +1202,8 @@
       <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="8" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="7"/>
@@ -1158,7 +1240,7 @@
       <c r="D5" s="7">
         <v>5.0</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F5" s="7"/>
@@ -1188,7 +1270,7 @@
       <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1229,7 +1311,7 @@
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="7"/>
@@ -1268,7 +1350,7 @@
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="7"/>
@@ -1307,7 +1389,7 @@
       <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="7"/>
@@ -1385,7 +1467,7 @@
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -1465,7 +1547,7 @@
       <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -1504,7 +1586,7 @@
       <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="7"/>
@@ -1539,7 +1621,7 @@
       <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -1576,15 +1658,13 @@
       <c r="A16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1613,13 +1693,13 @@
       <c r="A17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>22</v>
+      <c r="B17" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -1645,16 +1725,16 @@
       <c r="AA17" s="7"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>25</v>
+      <c r="B18" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="7" t="s">
-        <v>54</v>
+      <c r="E18" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1683,15 +1763,15 @@
       <c r="A19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -1718,7 +1798,7 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>22</v>
@@ -1726,7 +1806,7 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1753,19 +1833,19 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21" s="7">
         <v>1.0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -1792,22 +1872,24 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>22</v>
+      <c r="B22" s="7" t="s">
+        <v>18</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -1831,24 +1913,22 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="7">
         <v>5.0</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>65</v>
+      <c r="E23" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="F23" s="7"/>
-      <c r="G23" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
@@ -1872,22 +1952,22 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>22</v>
+      <c r="B24" s="9" t="s">
+        <v>25</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>67</v>
-      </c>
+      <c r="C24" s="7"/>
       <c r="D24" s="7">
         <v>5.0</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
@@ -1911,22 +1991,22 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>22</v>
+      <c r="B25" s="9" t="s">
+        <v>25</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>69</v>
-      </c>
+      <c r="C25" s="7"/>
       <c r="D25" s="7">
         <v>5.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
@@ -1950,20 +2030,22 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>22</v>
+      <c r="B26" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7">
         <v>5.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="G26" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
@@ -1987,17 +2069,19 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>22</v>
+      <c r="B27" s="7" t="s">
+        <v>35</v>
       </c>
-      <c r="C27" s="7"/>
+      <c r="C27" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="D27" s="7">
         <v>5.0</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -2024,22 +2108,20 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>25</v>
+      <c r="B28" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7">
         <v>5.0</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
-        <v>70</v>
-      </c>
+      <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
@@ -2063,22 +2145,20 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>25</v>
+      <c r="B29" s="9" t="s">
+        <v>22</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="C29" s="12" t="s">
         <v>74</v>
       </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="F29" s="7"/>
-      <c r="G29" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
@@ -2101,23 +2181,19 @@
       <c r="AA29" s="7"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>59</v>
+      <c r="A30" s="11" t="s">
+        <v>76</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>25</v>
+      <c r="B30" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C30" s="7"/>
-      <c r="D30" s="7">
-        <v>5.0</v>
-      </c>
+      <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F30" s="7"/>
-      <c r="G30" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
@@ -2141,19 +2217,15 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="7">
-        <v>5.0</v>
+      <c r="B31" s="9" t="s">
+        <v>22</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>66</v>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -2180,17 +2252,17 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>35</v>
+      <c r="B32" s="9" t="s">
+        <v>22</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7">
-        <v>5.0</v>
+      <c r="C32" s="7" t="s">
+        <v>80</v>
       </c>
+      <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -2217,17 +2289,15 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="11" t="s">
         <v>79</v>
       </c>
+      <c r="B33" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -2254,15 +2324,15 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>35</v>
+      <c r="B34" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -2289,18 +2359,22 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>50</v>
+      <c r="B35" s="9" t="s">
+        <v>25</v>
       </c>
-      <c r="C35" s="7"/>
+      <c r="C35" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="G35" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
@@ -2324,22 +2398,20 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>22</v>
+      <c r="B36" s="9" t="s">
+        <v>25</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="7">
-        <v>5.0</v>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="s">
+        <v>82</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
@@ -2363,20 +2435,20 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>22</v>
+      <c r="B37" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C37" s="7"/>
-      <c r="D37" s="7">
-        <v>5.0</v>
-      </c>
+      <c r="D37" s="7"/>
       <c r="E37" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="G37" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
@@ -2400,17 +2472,17 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>22</v>
+      <c r="B38" s="7" t="s">
+        <v>35</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7">
-        <v>5.0</v>
+      <c r="C38" s="7" t="s">
+        <v>87</v>
       </c>
+      <c r="D38" s="7"/>
       <c r="E38" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -2437,24 +2509,20 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>25</v>
+      <c r="B39" s="9" t="s">
+        <v>22</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="7">
-        <v>5.0</v>
-      </c>
+      <c r="D39" s="7"/>
       <c r="E39" s="7" t="s">
         <v>91</v>
       </c>
       <c r="F39" s="7"/>
-      <c r="G39" s="7" t="s">
-        <v>87</v>
-      </c>
+      <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
@@ -2478,22 +2546,18 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>25</v>
+      <c r="B40" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="7">
-        <v>5.0</v>
-      </c>
+      <c r="D40" s="7"/>
       <c r="E40" s="7" t="s">
         <v>92</v>
       </c>
       <c r="F40" s="7"/>
-      <c r="G40" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
@@ -2517,22 +2581,20 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>25</v>
+      <c r="B41" s="7" t="s">
+        <v>15</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7">
-        <v>5.0</v>
+      <c r="C41" s="7" t="s">
+        <v>94</v>
       </c>
+      <c r="D41" s="7"/>
       <c r="E41" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F41" s="7"/>
-      <c r="G41" s="7" t="s">
-        <v>89</v>
-      </c>
+      <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
@@ -2556,19 +2618,17 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
-      <c r="D42" s="7">
-        <v>5.0</v>
-      </c>
+      <c r="D42" s="7"/>
       <c r="E42" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -2594,18 +2654,16 @@
       <c r="AA42" s="7"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="6" t="s">
-        <v>95</v>
+      <c r="A43" s="11" t="s">
+        <v>98</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>50</v>
+      <c r="B43" s="9" t="s">
+        <v>35</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>96</v>
-      </c>
+      <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7" t="s">
-        <v>97</v>
+      <c r="E43" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
@@ -2631,16 +2689,16 @@
       <c r="AA43" s="7"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6" t="s">
-        <v>95</v>
+      <c r="A44" s="11" t="s">
+        <v>98</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>35</v>
+      <c r="B44" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="7" t="s">
-        <v>98</v>
+      <c r="E44" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -2666,19 +2724,15 @@
       <c r="AA44" s="7"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="6" t="s">
-        <v>99</v>
+      <c r="A45" s="11" t="s">
+        <v>98</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>15</v>
+      <c r="B45" s="9" t="s">
+        <v>22</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="E45" s="7" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="8" t="s">
         <v>101</v>
       </c>
       <c r="F45" s="7"/>
@@ -2705,20 +2759,16 @@
       <c r="AA45" s="7"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
-        <v>99</v>
+      <c r="A46" s="11" t="s">
+        <v>98</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>35</v>
+      <c r="B46" s="9" t="s">
+        <v>22</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="D46" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -2744,11 +2794,17 @@
       <c r="AA46" s="7"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
+      <c r="A47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+      <c r="E47" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -2773,11 +2829,17 @@
       <c r="AA47" s="7"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="E48" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -2802,11 +2864,17 @@
       <c r="AA48" s="7"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
+      <c r="A49" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
+      <c r="E49" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -2831,11 +2899,17 @@
       <c r="AA49" s="7"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="7"/>
+      <c r="A50" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
+      <c r="E50" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -2860,11 +2934,17 @@
       <c r="AA50" s="7"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
+      <c r="E51" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -2889,11 +2969,17 @@
       <c r="AA51" s="7"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
+      <c r="A52" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
+      <c r="E52" s="8" t="s">
+        <v>111</v>
+      </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -2918,11 +3004,17 @@
       <c r="AA52" s="7"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7"/>
+      <c r="A53" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="E53" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
@@ -2947,11 +3039,17 @@
       <c r="AA53" s="7"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="7"/>
+      <c r="A54" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="E54" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -30322,135 +30420,37 @@
       <c r="Z997" s="7"/>
       <c r="AA997" s="7"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="6"/>
-      <c r="B998" s="7"/>
-      <c r="C998" s="7"/>
-      <c r="D998" s="7"/>
-      <c r="E998" s="7"/>
-      <c r="F998" s="7"/>
-      <c r="G998" s="7"/>
-      <c r="H998" s="7"/>
-      <c r="I998" s="7"/>
-      <c r="J998" s="7"/>
-      <c r="K998" s="7"/>
-      <c r="L998" s="7"/>
-      <c r="M998" s="7"/>
-      <c r="N998" s="7"/>
-      <c r="O998" s="7"/>
-      <c r="P998" s="7"/>
-      <c r="Q998" s="7"/>
-      <c r="R998" s="7"/>
-      <c r="S998" s="7"/>
-      <c r="T998" s="7"/>
-      <c r="U998" s="7"/>
-      <c r="V998" s="7"/>
-      <c r="W998" s="7"/>
-      <c r="X998" s="7"/>
-      <c r="Y998" s="7"/>
-      <c r="Z998" s="7"/>
-      <c r="AA998" s="7"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="6"/>
-      <c r="B999" s="7"/>
-      <c r="C999" s="7"/>
-      <c r="D999" s="7"/>
-      <c r="E999" s="7"/>
-      <c r="F999" s="7"/>
-      <c r="G999" s="7"/>
-      <c r="H999" s="7"/>
-      <c r="I999" s="7"/>
-      <c r="J999" s="7"/>
-      <c r="K999" s="7"/>
-      <c r="L999" s="7"/>
-      <c r="M999" s="7"/>
-      <c r="N999" s="7"/>
-      <c r="O999" s="7"/>
-      <c r="P999" s="7"/>
-      <c r="Q999" s="7"/>
-      <c r="R999" s="7"/>
-      <c r="S999" s="7"/>
-      <c r="T999" s="7"/>
-      <c r="U999" s="7"/>
-      <c r="V999" s="7"/>
-      <c r="W999" s="7"/>
-      <c r="X999" s="7"/>
-      <c r="Y999" s="7"/>
-      <c r="Z999" s="7"/>
-      <c r="AA999" s="7"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="6"/>
-      <c r="B1000" s="7"/>
-      <c r="C1000" s="7"/>
-      <c r="D1000" s="7"/>
-      <c r="E1000" s="7"/>
-      <c r="F1000" s="7"/>
-      <c r="G1000" s="7"/>
-      <c r="H1000" s="7"/>
-      <c r="I1000" s="7"/>
-      <c r="J1000" s="7"/>
-      <c r="K1000" s="7"/>
-      <c r="L1000" s="7"/>
-      <c r="M1000" s="7"/>
-      <c r="N1000" s="7"/>
-      <c r="O1000" s="7"/>
-      <c r="P1000" s="7"/>
-      <c r="Q1000" s="7"/>
-      <c r="R1000" s="7"/>
-      <c r="S1000" s="7"/>
-      <c r="T1000" s="7"/>
-      <c r="U1000" s="7"/>
-      <c r="V1000" s="7"/>
-      <c r="W1000" s="7"/>
-      <c r="X1000" s="7"/>
-      <c r="Y1000" s="7"/>
-      <c r="Z1000" s="7"/>
-      <c r="AA1000" s="7"/>
-    </row>
-    <row r="1001" ht="15.75" customHeight="1">
-      <c r="A1001" s="6"/>
-      <c r="B1001" s="7"/>
-      <c r="C1001" s="7"/>
-      <c r="D1001" s="7"/>
-      <c r="E1001" s="7"/>
-      <c r="F1001" s="7"/>
-      <c r="G1001" s="7"/>
-      <c r="H1001" s="7"/>
-      <c r="I1001" s="7"/>
-      <c r="J1001" s="7"/>
-      <c r="K1001" s="7"/>
-      <c r="L1001" s="7"/>
-      <c r="M1001" s="7"/>
-      <c r="N1001" s="7"/>
-      <c r="O1001" s="7"/>
-      <c r="P1001" s="7"/>
-      <c r="Q1001" s="7"/>
-      <c r="R1001" s="7"/>
-      <c r="S1001" s="7"/>
-      <c r="T1001" s="7"/>
-      <c r="U1001" s="7"/>
-      <c r="V1001" s="7"/>
-      <c r="W1001" s="7"/>
-      <c r="X1001" s="7"/>
-      <c r="Y1001" s="7"/>
-      <c r="Z1001" s="7"/>
-      <c r="AA1001" s="7"/>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B1001">
-      <formula1>"news,all_saving_accounts,regulated_savings,term_accounts,tarif_pdf,regulated_pdf,term_pdf"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B997">
+      <formula1>"news,regulated_savings,term_accounts,tarif_pdf,regulated_pdf,term_pdf"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="offre" ref="G4"/>
+    <hyperlink r:id="rId1" ref="E3"/>
+    <hyperlink r:id="rId2" location="offre" ref="G4"/>
+    <hyperlink r:id="rId3" ref="E5"/>
+    <hyperlink r:id="rId4" ref="E16"/>
+    <hyperlink r:id="rId5" ref="E18"/>
+    <hyperlink r:id="rId6" ref="E23"/>
+    <hyperlink r:id="rId7" ref="E31"/>
+    <hyperlink r:id="rId8" ref="E43"/>
+    <hyperlink r:id="rId9" ref="E44"/>
+    <hyperlink r:id="rId10" ref="E45"/>
+    <hyperlink r:id="rId11" ref="E46"/>
+    <hyperlink r:id="rId12" ref="E47"/>
+    <hyperlink r:id="rId13" ref="E48"/>
+    <hyperlink r:id="rId14" ref="E49"/>
+    <hyperlink r:id="rId15" ref="E50"/>
+    <hyperlink r:id="rId16" ref="E51"/>
+    <hyperlink r:id="rId17" ref="E52"/>
+    <hyperlink r:id="rId18" ref="E53"/>
+    <hyperlink r:id="rId19" ref="E54"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -30463,3282 +30463,3281 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="30.57"/>
     <col customWidth="1" min="2" max="2" width="46.57"/>
-    <col customWidth="1" min="3" max="3" width="68.86"/>
-    <col customWidth="1" min="4" max="4" width="23.86"/>
+    <col customWidth="1" min="3" max="3" width="57.86"/>
+    <col customWidth="1" min="4" max="4" width="61.57"/>
     <col customWidth="1" min="5" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>104</v>
+      <c r="B1" s="13" t="s">
+        <v>115</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>105</v>
+      <c r="C1" s="13" t="s">
+        <v>116</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>106</v>
+      <c r="B3" s="16" t="s">
+        <v>118</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>107</v>
+      <c r="C3" s="16" t="s">
+        <v>119</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>109</v>
+      <c r="B4" s="16" t="s">
+        <v>120</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>110</v>
+      <c r="C4" s="16" t="s">
+        <v>121</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>112</v>
+      <c r="B5" s="16" t="s">
+        <v>122</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>113</v>
+      <c r="C5" s="16" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="s">
+    <row r="6">
+      <c r="A6" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="s">
+      <c r="B7" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C7" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="14" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="14" t="s">
+      <c r="B8" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C8" s="16" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="s">
+    <row r="9">
+      <c r="A9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="C9" s="16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
+    <row r="10">
+      <c r="A10" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="C10" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="14" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
+      <c r="B11" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="C11" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="14" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="C12" s="16" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="s">
+    <row r="13">
+      <c r="A13" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>127</v>
+      <c r="B13" s="16" t="s">
+        <v>138</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C13" s="16" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
+    <row r="14">
+      <c r="A14" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="C14" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="14" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="14" t="s">
+      <c r="B15" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C15" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
+    <row r="16">
+      <c r="A16" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B19" s="14" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="B17" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="s">
+    <row r="18">
+      <c r="A18" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B18" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C18" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13" t="s">
+    <row r="19">
+      <c r="A19" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="C19" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="14" t="s">
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="13" t="s">
+      <c r="B20" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="C20" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="14" t="s">
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="13" t="s">
+      <c r="B21" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="14" t="s">
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="15" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="13" t="s">
+      <c r="B22" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="C22" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="14" t="s">
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="15" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="13" t="s">
+      <c r="B23" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="C23" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="14" t="s">
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="15" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="13" t="s">
+      <c r="B24" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="C24" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C26" s="14" t="s">
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="15" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="B25" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="C25" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="C27" s="14" t="s">
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="15" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" s="14" t="s">
+      <c r="B26" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C26" s="16" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="13" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B27" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C27" s="16" t="s">
         <v>178</v>
       </c>
     </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="13"/>
+      <c r="A32" s="15"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="13"/>
+      <c r="A33" s="15"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="13"/>
+      <c r="A34" s="15"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="13"/>
+      <c r="A35" s="15"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="13"/>
+      <c r="A36" s="15"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="13"/>
+      <c r="A37" s="15"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="13"/>
+      <c r="A38" s="15"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="13"/>
+      <c r="A39" s="15"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="13"/>
+      <c r="A40" s="15"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="13"/>
+      <c r="A41" s="15"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="13"/>
+      <c r="A42" s="15"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13"/>
+      <c r="A43" s="15"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="13"/>
+      <c r="A44" s="15"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="13"/>
+      <c r="A45" s="15"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="13"/>
+      <c r="A46" s="15"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="13"/>
+      <c r="A47" s="15"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="13"/>
+      <c r="A48" s="15"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="13"/>
+      <c r="A49" s="15"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="13"/>
+      <c r="A50" s="15"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="13"/>
+      <c r="A51" s="15"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="13"/>
+      <c r="A52" s="15"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="13"/>
+      <c r="A53" s="15"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="13"/>
+      <c r="A54" s="15"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="13"/>
+      <c r="A55" s="15"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="13"/>
+      <c r="A56" s="15"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="13"/>
+      <c r="A57" s="15"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="13"/>
+      <c r="A58" s="15"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="13"/>
+      <c r="A59" s="15"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="13"/>
+      <c r="A60" s="15"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="13"/>
+      <c r="A61" s="15"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="13"/>
+      <c r="A62" s="15"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="13"/>
+      <c r="A63" s="15"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="13"/>
+      <c r="A64" s="15"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="13"/>
+      <c r="A65" s="15"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="13"/>
+      <c r="A66" s="15"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="13"/>
+      <c r="A67" s="15"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="13"/>
+      <c r="A68" s="15"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="13"/>
+      <c r="A69" s="15"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="13"/>
+      <c r="A70" s="15"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="13"/>
+      <c r="A71" s="15"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="13"/>
+      <c r="A72" s="15"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="13"/>
+      <c r="A73" s="15"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="13"/>
+      <c r="A74" s="15"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="13"/>
+      <c r="A75" s="15"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="13"/>
+      <c r="A76" s="15"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="13"/>
+      <c r="A77" s="15"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="13"/>
+      <c r="A78" s="15"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="13"/>
+      <c r="A79" s="15"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="13"/>
+      <c r="A80" s="15"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="13"/>
+      <c r="A81" s="15"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="13"/>
+      <c r="A82" s="15"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="13"/>
+      <c r="A83" s="15"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="13"/>
+      <c r="A84" s="15"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="13"/>
+      <c r="A85" s="15"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="13"/>
+      <c r="A86" s="15"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="13"/>
+      <c r="A87" s="15"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="13"/>
+      <c r="A88" s="15"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="13"/>
+      <c r="A89" s="15"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="13"/>
+      <c r="A90" s="15"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="13"/>
+      <c r="A91" s="15"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="13"/>
+      <c r="A92" s="15"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="13"/>
+      <c r="A93" s="15"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="13"/>
+      <c r="A94" s="15"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="13"/>
+      <c r="A95" s="15"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="13"/>
+      <c r="A96" s="15"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="13"/>
+      <c r="A97" s="15"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="13"/>
+      <c r="A98" s="15"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="13"/>
+      <c r="A99" s="15"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="13"/>
+      <c r="A100" s="15"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="13"/>
+      <c r="A101" s="15"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="13"/>
+      <c r="A102" s="15"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="13"/>
+      <c r="A103" s="15"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="13"/>
+      <c r="A104" s="15"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="13"/>
+      <c r="A105" s="15"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="13"/>
+      <c r="A106" s="15"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="13"/>
+      <c r="A107" s="15"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="13"/>
+      <c r="A108" s="15"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="13"/>
+      <c r="A109" s="15"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="13"/>
+      <c r="A110" s="15"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="13"/>
+      <c r="A111" s="15"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="13"/>
+      <c r="A112" s="15"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="13"/>
+      <c r="A113" s="15"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="13"/>
+      <c r="A114" s="15"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="13"/>
+      <c r="A115" s="15"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="13"/>
+      <c r="A116" s="15"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="13"/>
+      <c r="A117" s="15"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="13"/>
+      <c r="A118" s="15"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="13"/>
+      <c r="A119" s="15"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="13"/>
+      <c r="A120" s="15"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="13"/>
+      <c r="A121" s="15"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="13"/>
+      <c r="A122" s="15"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="13"/>
+      <c r="A123" s="15"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="13"/>
+      <c r="A124" s="15"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="13"/>
+      <c r="A125" s="15"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="13"/>
+      <c r="A126" s="15"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="13"/>
+      <c r="A127" s="15"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="13"/>
+      <c r="A128" s="15"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="13"/>
+      <c r="A129" s="15"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="13"/>
+      <c r="A130" s="15"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="13"/>
+      <c r="A131" s="15"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="13"/>
+      <c r="A132" s="15"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="13"/>
+      <c r="A133" s="15"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="13"/>
+      <c r="A134" s="15"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="13"/>
+      <c r="A135" s="15"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="13"/>
+      <c r="A136" s="15"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="13"/>
+      <c r="A137" s="15"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="13"/>
+      <c r="A138" s="15"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="13"/>
+      <c r="A139" s="15"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="13"/>
+      <c r="A140" s="15"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="13"/>
+      <c r="A141" s="15"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="13"/>
+      <c r="A142" s="15"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="13"/>
+      <c r="A143" s="15"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="13"/>
+      <c r="A144" s="15"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="13"/>
+      <c r="A145" s="15"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="13"/>
+      <c r="A146" s="15"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="13"/>
+      <c r="A147" s="15"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="13"/>
+      <c r="A148" s="15"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="13"/>
+      <c r="A149" s="15"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="13"/>
+      <c r="A150" s="15"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="13"/>
+      <c r="A151" s="15"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="13"/>
+      <c r="A152" s="15"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="13"/>
+      <c r="A153" s="15"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="13"/>
+      <c r="A154" s="15"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="13"/>
+      <c r="A155" s="15"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="13"/>
+      <c r="A156" s="15"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="13"/>
+      <c r="A157" s="15"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="13"/>
+      <c r="A158" s="15"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="13"/>
+      <c r="A159" s="15"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="13"/>
+      <c r="A160" s="15"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="13"/>
+      <c r="A161" s="15"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="13"/>
+      <c r="A162" s="15"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="13"/>
+      <c r="A163" s="15"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="13"/>
+      <c r="A164" s="15"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="13"/>
+      <c r="A165" s="15"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="13"/>
+      <c r="A166" s="15"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="13"/>
+      <c r="A167" s="15"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="13"/>
+      <c r="A168" s="15"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="13"/>
+      <c r="A169" s="15"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="13"/>
+      <c r="A170" s="15"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="13"/>
+      <c r="A171" s="15"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="13"/>
+      <c r="A172" s="15"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="13"/>
+      <c r="A173" s="15"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="13"/>
+      <c r="A174" s="15"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="13"/>
+      <c r="A175" s="15"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="13"/>
+      <c r="A176" s="15"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="13"/>
+      <c r="A177" s="15"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="13"/>
+      <c r="A178" s="15"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="13"/>
+      <c r="A179" s="15"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="13"/>
+      <c r="A180" s="15"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="13"/>
+      <c r="A181" s="15"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="13"/>
+      <c r="A182" s="15"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="13"/>
+      <c r="A183" s="15"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="13"/>
+      <c r="A184" s="15"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="13"/>
+      <c r="A185" s="15"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="13"/>
+      <c r="A186" s="15"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="13"/>
+      <c r="A187" s="15"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="13"/>
+      <c r="A188" s="15"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="13"/>
+      <c r="A189" s="15"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="13"/>
+      <c r="A190" s="15"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="13"/>
+      <c r="A191" s="15"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="13"/>
+      <c r="A192" s="15"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="13"/>
+      <c r="A193" s="15"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="13"/>
+      <c r="A194" s="15"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="13"/>
+      <c r="A195" s="15"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="13"/>
+      <c r="A196" s="15"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="13"/>
+      <c r="A197" s="15"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="13"/>
+      <c r="A198" s="15"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="13"/>
+      <c r="A199" s="15"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="13"/>
+      <c r="A200" s="15"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="13"/>
+      <c r="A201" s="15"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="13"/>
+      <c r="A202" s="15"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="13"/>
+      <c r="A203" s="15"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="13"/>
+      <c r="A204" s="15"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="13"/>
+      <c r="A205" s="15"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="13"/>
+      <c r="A206" s="15"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="13"/>
+      <c r="A207" s="15"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="13"/>
+      <c r="A208" s="15"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="13"/>
+      <c r="A209" s="15"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="13"/>
+      <c r="A210" s="15"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="13"/>
+      <c r="A211" s="15"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="13"/>
+      <c r="A212" s="15"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="13"/>
+      <c r="A213" s="15"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="13"/>
+      <c r="A214" s="15"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="13"/>
+      <c r="A215" s="15"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="13"/>
+      <c r="A216" s="15"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="13"/>
+      <c r="A217" s="15"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="13"/>
+      <c r="A218" s="15"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="13"/>
+      <c r="A219" s="15"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="13"/>
+      <c r="A220" s="15"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="13"/>
+      <c r="A221" s="15"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="13"/>
+      <c r="A222" s="15"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="13"/>
+      <c r="A223" s="15"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="13"/>
+      <c r="A224" s="15"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="13"/>
+      <c r="A225" s="15"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="13"/>
+      <c r="A226" s="15"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="13"/>
+      <c r="A227" s="15"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="13"/>
+      <c r="A228" s="15"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="13"/>
+      <c r="A229" s="15"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="13"/>
+      <c r="A230" s="15"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="13"/>
+      <c r="A231" s="15"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="13"/>
+      <c r="A232" s="15"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="13"/>
+      <c r="A233" s="15"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="13"/>
+      <c r="A234" s="15"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="13"/>
+      <c r="A235" s="15"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="13"/>
+      <c r="A236" s="15"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="13"/>
+      <c r="A237" s="15"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="13"/>
+      <c r="A238" s="15"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="13"/>
+      <c r="A239" s="15"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="13"/>
+      <c r="A240" s="15"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="13"/>
+      <c r="A241" s="15"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="13"/>
+      <c r="A242" s="15"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="13"/>
+      <c r="A243" s="15"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="13"/>
+      <c r="A244" s="15"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="13"/>
+      <c r="A245" s="15"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="13"/>
+      <c r="A246" s="15"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="13"/>
+      <c r="A247" s="15"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="13"/>
+      <c r="A248" s="15"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="13"/>
+      <c r="A249" s="15"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="13"/>
+      <c r="A250" s="15"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="13"/>
+      <c r="A251" s="15"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="13"/>
+      <c r="A252" s="15"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="13"/>
+      <c r="A253" s="15"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="13"/>
+      <c r="A254" s="15"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="13"/>
+      <c r="A255" s="15"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="13"/>
+      <c r="A256" s="15"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="13"/>
+      <c r="A257" s="15"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="13"/>
+      <c r="A258" s="15"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="13"/>
+      <c r="A259" s="15"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="13"/>
+      <c r="A260" s="15"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="13"/>
+      <c r="A261" s="15"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="13"/>
+      <c r="A262" s="15"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="13"/>
+      <c r="A263" s="15"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="13"/>
+      <c r="A264" s="15"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="13"/>
+      <c r="A265" s="15"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="13"/>
+      <c r="A266" s="15"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="13"/>
+      <c r="A267" s="15"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="13"/>
+      <c r="A268" s="15"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="13"/>
+      <c r="A269" s="15"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="13"/>
+      <c r="A270" s="15"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="13"/>
+      <c r="A271" s="15"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="13"/>
+      <c r="A272" s="15"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="13"/>
+      <c r="A273" s="15"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="13"/>
+      <c r="A274" s="15"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="13"/>
+      <c r="A275" s="15"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="13"/>
+      <c r="A276" s="15"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="13"/>
+      <c r="A277" s="15"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="13"/>
+      <c r="A278" s="15"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="13"/>
+      <c r="A279" s="15"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="13"/>
+      <c r="A280" s="15"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="13"/>
+      <c r="A281" s="15"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="13"/>
+      <c r="A282" s="15"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="13"/>
+      <c r="A283" s="15"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="13"/>
+      <c r="A284" s="15"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="13"/>
+      <c r="A285" s="15"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="13"/>
+      <c r="A286" s="15"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="13"/>
+      <c r="A287" s="15"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="13"/>
+      <c r="A288" s="15"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="13"/>
+      <c r="A289" s="15"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="13"/>
+      <c r="A290" s="15"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="13"/>
+      <c r="A291" s="15"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="13"/>
+      <c r="A292" s="15"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="13"/>
+      <c r="A293" s="15"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="13"/>
+      <c r="A294" s="15"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="13"/>
+      <c r="A295" s="15"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="13"/>
+      <c r="A296" s="15"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="13"/>
+      <c r="A297" s="15"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="13"/>
+      <c r="A298" s="15"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="13"/>
+      <c r="A299" s="15"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="13"/>
+      <c r="A300" s="15"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="13"/>
+      <c r="A301" s="15"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="13"/>
+      <c r="A302" s="15"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="13"/>
+      <c r="A303" s="15"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="13"/>
+      <c r="A304" s="15"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="13"/>
+      <c r="A305" s="15"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="13"/>
+      <c r="A306" s="15"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="13"/>
+      <c r="A307" s="15"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="13"/>
+      <c r="A308" s="15"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="13"/>
+      <c r="A309" s="15"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="13"/>
+      <c r="A310" s="15"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="13"/>
+      <c r="A311" s="15"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="13"/>
+      <c r="A312" s="15"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="13"/>
+      <c r="A313" s="15"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="13"/>
+      <c r="A314" s="15"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="13"/>
+      <c r="A315" s="15"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="13"/>
+      <c r="A316" s="15"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="13"/>
+      <c r="A317" s="15"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="13"/>
+      <c r="A318" s="15"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="13"/>
+      <c r="A319" s="15"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="13"/>
+      <c r="A320" s="15"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="13"/>
+      <c r="A321" s="15"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="13"/>
+      <c r="A322" s="15"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="13"/>
+      <c r="A323" s="15"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="13"/>
+      <c r="A324" s="15"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="13"/>
+      <c r="A325" s="15"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="13"/>
+      <c r="A326" s="15"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="13"/>
+      <c r="A327" s="15"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="13"/>
+      <c r="A328" s="15"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="13"/>
+      <c r="A329" s="15"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="13"/>
+      <c r="A330" s="15"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="13"/>
+      <c r="A331" s="15"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="13"/>
+      <c r="A332" s="15"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="13"/>
+      <c r="A333" s="15"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="13"/>
+      <c r="A334" s="15"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="13"/>
+      <c r="A335" s="15"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="13"/>
+      <c r="A336" s="15"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="13"/>
+      <c r="A337" s="15"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="13"/>
+      <c r="A338" s="15"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="13"/>
+      <c r="A339" s="15"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="13"/>
+      <c r="A340" s="15"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="13"/>
+      <c r="A341" s="15"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="13"/>
+      <c r="A342" s="15"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="13"/>
+      <c r="A343" s="15"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="13"/>
+      <c r="A344" s="15"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="13"/>
+      <c r="A345" s="15"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="13"/>
+      <c r="A346" s="15"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="13"/>
+      <c r="A347" s="15"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="13"/>
+      <c r="A348" s="15"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="13"/>
+      <c r="A349" s="15"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="13"/>
+      <c r="A350" s="15"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="13"/>
+      <c r="A351" s="15"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="13"/>
+      <c r="A352" s="15"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="13"/>
+      <c r="A353" s="15"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="13"/>
+      <c r="A354" s="15"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="13"/>
+      <c r="A355" s="15"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="13"/>
+      <c r="A356" s="15"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="13"/>
+      <c r="A357" s="15"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="13"/>
+      <c r="A358" s="15"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="13"/>
+      <c r="A359" s="15"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="13"/>
+      <c r="A360" s="15"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="13"/>
+      <c r="A361" s="15"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="13"/>
+      <c r="A362" s="15"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="13"/>
+      <c r="A363" s="15"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="13"/>
+      <c r="A364" s="15"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="13"/>
+      <c r="A365" s="15"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="13"/>
+      <c r="A366" s="15"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="13"/>
+      <c r="A367" s="15"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="13"/>
+      <c r="A368" s="15"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="13"/>
+      <c r="A369" s="15"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="13"/>
+      <c r="A370" s="15"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="13"/>
+      <c r="A371" s="15"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="13"/>
+      <c r="A372" s="15"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="13"/>
+      <c r="A373" s="15"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="13"/>
+      <c r="A374" s="15"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="13"/>
+      <c r="A375" s="15"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="13"/>
+      <c r="A376" s="15"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="13"/>
+      <c r="A377" s="15"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="13"/>
+      <c r="A378" s="15"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="13"/>
+      <c r="A379" s="15"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="13"/>
+      <c r="A380" s="15"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="13"/>
+      <c r="A381" s="15"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="13"/>
+      <c r="A382" s="15"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="13"/>
+      <c r="A383" s="15"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="13"/>
+      <c r="A384" s="15"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="13"/>
+      <c r="A385" s="15"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="13"/>
+      <c r="A386" s="15"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="13"/>
+      <c r="A387" s="15"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="13"/>
+      <c r="A388" s="15"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="13"/>
+      <c r="A389" s="15"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="13"/>
+      <c r="A390" s="15"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="13"/>
+      <c r="A391" s="15"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="13"/>
+      <c r="A392" s="15"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="13"/>
+      <c r="A393" s="15"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="13"/>
+      <c r="A394" s="15"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="13"/>
+      <c r="A395" s="15"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="13"/>
+      <c r="A396" s="15"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="13"/>
+      <c r="A397" s="15"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="13"/>
+      <c r="A398" s="15"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="13"/>
+      <c r="A399" s="15"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="13"/>
+      <c r="A400" s="15"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="13"/>
+      <c r="A401" s="15"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="13"/>
+      <c r="A402" s="15"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="13"/>
+      <c r="A403" s="15"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="13"/>
+      <c r="A404" s="15"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="13"/>
+      <c r="A405" s="15"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="13"/>
+      <c r="A406" s="15"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="13"/>
+      <c r="A407" s="15"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="13"/>
+      <c r="A408" s="15"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="13"/>
+      <c r="A409" s="15"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="13"/>
+      <c r="A410" s="15"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="13"/>
+      <c r="A411" s="15"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="13"/>
+      <c r="A412" s="15"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="13"/>
+      <c r="A413" s="15"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="13"/>
+      <c r="A414" s="15"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="13"/>
+      <c r="A415" s="15"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="13"/>
+      <c r="A416" s="15"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="13"/>
+      <c r="A417" s="15"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="13"/>
+      <c r="A418" s="15"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="13"/>
+      <c r="A419" s="15"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="13"/>
+      <c r="A420" s="15"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="13"/>
+      <c r="A421" s="15"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="13"/>
+      <c r="A422" s="15"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="13"/>
+      <c r="A423" s="15"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="13"/>
+      <c r="A424" s="15"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="13"/>
+      <c r="A425" s="15"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="13"/>
+      <c r="A426" s="15"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="13"/>
+      <c r="A427" s="15"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="13"/>
+      <c r="A428" s="15"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="13"/>
+      <c r="A429" s="15"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="13"/>
+      <c r="A430" s="15"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="13"/>
+      <c r="A431" s="15"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="13"/>
+      <c r="A432" s="15"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="13"/>
+      <c r="A433" s="15"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="13"/>
+      <c r="A434" s="15"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="13"/>
+      <c r="A435" s="15"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="13"/>
+      <c r="A436" s="15"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="13"/>
+      <c r="A437" s="15"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="13"/>
+      <c r="A438" s="15"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="13"/>
+      <c r="A439" s="15"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="13"/>
+      <c r="A440" s="15"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="13"/>
+      <c r="A441" s="15"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="13"/>
+      <c r="A442" s="15"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="13"/>
+      <c r="A443" s="15"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="13"/>
+      <c r="A444" s="15"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="13"/>
+      <c r="A445" s="15"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="13"/>
+      <c r="A446" s="15"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="13"/>
+      <c r="A447" s="15"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="13"/>
+      <c r="A448" s="15"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="13"/>
+      <c r="A449" s="15"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="13"/>
+      <c r="A450" s="15"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="13"/>
+      <c r="A451" s="15"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="13"/>
+      <c r="A452" s="15"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="13"/>
+      <c r="A453" s="15"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="13"/>
+      <c r="A454" s="15"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="13"/>
+      <c r="A455" s="15"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="13"/>
+      <c r="A456" s="15"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="13"/>
+      <c r="A457" s="15"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="13"/>
+      <c r="A458" s="15"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="13"/>
+      <c r="A459" s="15"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="13"/>
+      <c r="A460" s="15"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="13"/>
+      <c r="A461" s="15"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="13"/>
+      <c r="A462" s="15"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="13"/>
+      <c r="A463" s="15"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="13"/>
+      <c r="A464" s="15"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="13"/>
+      <c r="A465" s="15"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="13"/>
+      <c r="A466" s="15"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="13"/>
+      <c r="A467" s="15"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="13"/>
+      <c r="A468" s="15"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="13"/>
+      <c r="A469" s="15"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="13"/>
+      <c r="A470" s="15"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="13"/>
+      <c r="A471" s="15"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="13"/>
+      <c r="A472" s="15"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="13"/>
+      <c r="A473" s="15"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="13"/>
+      <c r="A474" s="15"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="13"/>
+      <c r="A475" s="15"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="13"/>
+      <c r="A476" s="15"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="13"/>
+      <c r="A477" s="15"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="13"/>
+      <c r="A478" s="15"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="13"/>
+      <c r="A479" s="15"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="13"/>
+      <c r="A480" s="15"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="13"/>
+      <c r="A481" s="15"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="13"/>
+      <c r="A482" s="15"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="13"/>
+      <c r="A483" s="15"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="13"/>
+      <c r="A484" s="15"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="13"/>
+      <c r="A485" s="15"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="13"/>
+      <c r="A486" s="15"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="13"/>
+      <c r="A487" s="15"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="13"/>
+      <c r="A488" s="15"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="13"/>
+      <c r="A489" s="15"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="13"/>
+      <c r="A490" s="15"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="13"/>
+      <c r="A491" s="15"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="13"/>
+      <c r="A492" s="15"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="13"/>
+      <c r="A493" s="15"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="13"/>
+      <c r="A494" s="15"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="13"/>
+      <c r="A495" s="15"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="13"/>
+      <c r="A496" s="15"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="13"/>
+      <c r="A497" s="15"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="13"/>
+      <c r="A498" s="15"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="13"/>
+      <c r="A499" s="15"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="13"/>
+      <c r="A500" s="15"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="13"/>
+      <c r="A501" s="15"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="13"/>
+      <c r="A502" s="15"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="13"/>
+      <c r="A503" s="15"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="13"/>
+      <c r="A504" s="15"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="13"/>
+      <c r="A505" s="15"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="13"/>
+      <c r="A506" s="15"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="13"/>
+      <c r="A507" s="15"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="13"/>
+      <c r="A508" s="15"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="13"/>
+      <c r="A509" s="15"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="13"/>
+      <c r="A510" s="15"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="13"/>
+      <c r="A511" s="15"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="13"/>
+      <c r="A512" s="15"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="13"/>
+      <c r="A513" s="15"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="13"/>
+      <c r="A514" s="15"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="13"/>
+      <c r="A515" s="15"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="13"/>
+      <c r="A516" s="15"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="13"/>
+      <c r="A517" s="15"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="13"/>
+      <c r="A518" s="15"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="13"/>
+      <c r="A519" s="15"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="13"/>
+      <c r="A520" s="15"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="13"/>
+      <c r="A521" s="15"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="13"/>
+      <c r="A522" s="15"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="13"/>
+      <c r="A523" s="15"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="13"/>
+      <c r="A524" s="15"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="13"/>
+      <c r="A525" s="15"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="13"/>
+      <c r="A526" s="15"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="13"/>
+      <c r="A527" s="15"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="13"/>
+      <c r="A528" s="15"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="13"/>
+      <c r="A529" s="15"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="13"/>
+      <c r="A530" s="15"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="13"/>
+      <c r="A531" s="15"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="13"/>
+      <c r="A532" s="15"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="13"/>
+      <c r="A533" s="15"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="13"/>
+      <c r="A534" s="15"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="13"/>
+      <c r="A535" s="15"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="13"/>
+      <c r="A536" s="15"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="13"/>
+      <c r="A537" s="15"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="13"/>
+      <c r="A538" s="15"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="13"/>
+      <c r="A539" s="15"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="13"/>
+      <c r="A540" s="15"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="13"/>
+      <c r="A541" s="15"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="13"/>
+      <c r="A542" s="15"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="13"/>
+      <c r="A543" s="15"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="13"/>
+      <c r="A544" s="15"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="13"/>
+      <c r="A545" s="15"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="13"/>
+      <c r="A546" s="15"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="13"/>
+      <c r="A547" s="15"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="13"/>
+      <c r="A548" s="15"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="13"/>
+      <c r="A549" s="15"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="13"/>
+      <c r="A550" s="15"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="13"/>
+      <c r="A551" s="15"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="13"/>
+      <c r="A552" s="15"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="13"/>
+      <c r="A553" s="15"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="13"/>
+      <c r="A554" s="15"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="13"/>
+      <c r="A555" s="15"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="13"/>
+      <c r="A556" s="15"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="13"/>
+      <c r="A557" s="15"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="13"/>
+      <c r="A558" s="15"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="13"/>
+      <c r="A559" s="15"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="13"/>
+      <c r="A560" s="15"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="13"/>
+      <c r="A561" s="15"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="13"/>
+      <c r="A562" s="15"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="13"/>
+      <c r="A563" s="15"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="13"/>
+      <c r="A564" s="15"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="13"/>
+      <c r="A565" s="15"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="13"/>
+      <c r="A566" s="15"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="13"/>
+      <c r="A567" s="15"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="13"/>
+      <c r="A568" s="15"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="13"/>
+      <c r="A569" s="15"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="13"/>
+      <c r="A570" s="15"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="13"/>
+      <c r="A571" s="15"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="13"/>
+      <c r="A572" s="15"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="13"/>
+      <c r="A573" s="15"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="13"/>
+      <c r="A574" s="15"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="13"/>
+      <c r="A575" s="15"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="13"/>
+      <c r="A576" s="15"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="13"/>
+      <c r="A577" s="15"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="13"/>
+      <c r="A578" s="15"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="13"/>
+      <c r="A579" s="15"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="13"/>
+      <c r="A580" s="15"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="13"/>
+      <c r="A581" s="15"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="13"/>
+      <c r="A582" s="15"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="13"/>
+      <c r="A583" s="15"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="13"/>
+      <c r="A584" s="15"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="13"/>
+      <c r="A585" s="15"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="13"/>
+      <c r="A586" s="15"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="13"/>
+      <c r="A587" s="15"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="13"/>
+      <c r="A588" s="15"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="13"/>
+      <c r="A589" s="15"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="13"/>
+      <c r="A590" s="15"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="13"/>
+      <c r="A591" s="15"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="13"/>
+      <c r="A592" s="15"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="13"/>
+      <c r="A593" s="15"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="13"/>
+      <c r="A594" s="15"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="13"/>
+      <c r="A595" s="15"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="13"/>
+      <c r="A596" s="15"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="13"/>
+      <c r="A597" s="15"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="13"/>
+      <c r="A598" s="15"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="13"/>
+      <c r="A599" s="15"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="13"/>
+      <c r="A600" s="15"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="13"/>
+      <c r="A601" s="15"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="13"/>
+      <c r="A602" s="15"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="13"/>
+      <c r="A603" s="15"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="13"/>
+      <c r="A604" s="15"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="13"/>
+      <c r="A605" s="15"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="13"/>
+      <c r="A606" s="15"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="13"/>
+      <c r="A607" s="15"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="13"/>
+      <c r="A608" s="15"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="13"/>
+      <c r="A609" s="15"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="13"/>
+      <c r="A610" s="15"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="13"/>
+      <c r="A611" s="15"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="13"/>
+      <c r="A612" s="15"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="13"/>
+      <c r="A613" s="15"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="13"/>
+      <c r="A614" s="15"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="13"/>
+      <c r="A615" s="15"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="13"/>
+      <c r="A616" s="15"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="13"/>
+      <c r="A617" s="15"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="13"/>
+      <c r="A618" s="15"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="13"/>
+      <c r="A619" s="15"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="13"/>
+      <c r="A620" s="15"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="13"/>
+      <c r="A621" s="15"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="13"/>
+      <c r="A622" s="15"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="13"/>
+      <c r="A623" s="15"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="13"/>
+      <c r="A624" s="15"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="13"/>
+      <c r="A625" s="15"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="13"/>
+      <c r="A626" s="15"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="13"/>
+      <c r="A627" s="15"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="13"/>
+      <c r="A628" s="15"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="13"/>
+      <c r="A629" s="15"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="13"/>
+      <c r="A630" s="15"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="13"/>
+      <c r="A631" s="15"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="13"/>
+      <c r="A632" s="15"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="13"/>
+      <c r="A633" s="15"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="13"/>
+      <c r="A634" s="15"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="13"/>
+      <c r="A635" s="15"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="13"/>
+      <c r="A636" s="15"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="13"/>
+      <c r="A637" s="15"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="13"/>
+      <c r="A638" s="15"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="13"/>
+      <c r="A639" s="15"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="13"/>
+      <c r="A640" s="15"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="13"/>
+      <c r="A641" s="15"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="13"/>
+      <c r="A642" s="15"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="13"/>
+      <c r="A643" s="15"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="13"/>
+      <c r="A644" s="15"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="13"/>
+      <c r="A645" s="15"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="13"/>
+      <c r="A646" s="15"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="13"/>
+      <c r="A647" s="15"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="13"/>
+      <c r="A648" s="15"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="13"/>
+      <c r="A649" s="15"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="13"/>
+      <c r="A650" s="15"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="13"/>
+      <c r="A651" s="15"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="13"/>
+      <c r="A652" s="15"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="13"/>
+      <c r="A653" s="15"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="13"/>
+      <c r="A654" s="15"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="13"/>
+      <c r="A655" s="15"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="13"/>
+      <c r="A656" s="15"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="13"/>
+      <c r="A657" s="15"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="13"/>
+      <c r="A658" s="15"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="13"/>
+      <c r="A659" s="15"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="13"/>
+      <c r="A660" s="15"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="13"/>
+      <c r="A661" s="15"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="13"/>
+      <c r="A662" s="15"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="13"/>
+      <c r="A663" s="15"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="13"/>
+      <c r="A664" s="15"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="13"/>
+      <c r="A665" s="15"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="13"/>
+      <c r="A666" s="15"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="13"/>
+      <c r="A667" s="15"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="13"/>
+      <c r="A668" s="15"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="13"/>
+      <c r="A669" s="15"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="13"/>
+      <c r="A670" s="15"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="13"/>
+      <c r="A671" s="15"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="13"/>
+      <c r="A672" s="15"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="13"/>
+      <c r="A673" s="15"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="13"/>
+      <c r="A674" s="15"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="13"/>
+      <c r="A675" s="15"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="13"/>
+      <c r="A676" s="15"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="13"/>
+      <c r="A677" s="15"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="13"/>
+      <c r="A678" s="15"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="13"/>
+      <c r="A679" s="15"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="13"/>
+      <c r="A680" s="15"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="13"/>
+      <c r="A681" s="15"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="13"/>
+      <c r="A682" s="15"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="13"/>
+      <c r="A683" s="15"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="13"/>
+      <c r="A684" s="15"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="13"/>
+      <c r="A685" s="15"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="13"/>
+      <c r="A686" s="15"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="13"/>
+      <c r="A687" s="15"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="13"/>
+      <c r="A688" s="15"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="13"/>
+      <c r="A689" s="15"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="13"/>
+      <c r="A690" s="15"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="13"/>
+      <c r="A691" s="15"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="13"/>
+      <c r="A692" s="15"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="13"/>
+      <c r="A693" s="15"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="13"/>
+      <c r="A694" s="15"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="13"/>
+      <c r="A695" s="15"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="13"/>
+      <c r="A696" s="15"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="13"/>
+      <c r="A697" s="15"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="13"/>
+      <c r="A698" s="15"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="13"/>
+      <c r="A699" s="15"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="13"/>
+      <c r="A700" s="15"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="13"/>
+      <c r="A701" s="15"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="13"/>
+      <c r="A702" s="15"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="13"/>
+      <c r="A703" s="15"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="13"/>
+      <c r="A704" s="15"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="13"/>
+      <c r="A705" s="15"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="13"/>
+      <c r="A706" s="15"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="13"/>
+      <c r="A707" s="15"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="13"/>
+      <c r="A708" s="15"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="13"/>
+      <c r="A709" s="15"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="13"/>
+      <c r="A710" s="15"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="13"/>
+      <c r="A711" s="15"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="13"/>
+      <c r="A712" s="15"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="13"/>
+      <c r="A713" s="15"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="13"/>
+      <c r="A714" s="15"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="13"/>
+      <c r="A715" s="15"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="13"/>
+      <c r="A716" s="15"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="13"/>
+      <c r="A717" s="15"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="13"/>
+      <c r="A718" s="15"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="13"/>
+      <c r="A719" s="15"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="13"/>
+      <c r="A720" s="15"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="13"/>
+      <c r="A721" s="15"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="13"/>
+      <c r="A722" s="15"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="13"/>
+      <c r="A723" s="15"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="13"/>
+      <c r="A724" s="15"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="13"/>
+      <c r="A725" s="15"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="13"/>
+      <c r="A726" s="15"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="13"/>
+      <c r="A727" s="15"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="13"/>
+      <c r="A728" s="15"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="13"/>
+      <c r="A729" s="15"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="13"/>
+      <c r="A730" s="15"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="13"/>
+      <c r="A731" s="15"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="13"/>
+      <c r="A732" s="15"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="13"/>
+      <c r="A733" s="15"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="13"/>
+      <c r="A734" s="15"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="13"/>
+      <c r="A735" s="15"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="13"/>
+      <c r="A736" s="15"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="13"/>
+      <c r="A737" s="15"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="13"/>
+      <c r="A738" s="15"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="13"/>
+      <c r="A739" s="15"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="13"/>
+      <c r="A740" s="15"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="13"/>
+      <c r="A741" s="15"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="13"/>
+      <c r="A742" s="15"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="13"/>
+      <c r="A743" s="15"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="13"/>
+      <c r="A744" s="15"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="13"/>
+      <c r="A745" s="15"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="13"/>
+      <c r="A746" s="15"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="13"/>
+      <c r="A747" s="15"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="13"/>
+      <c r="A748" s="15"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="13"/>
+      <c r="A749" s="15"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="13"/>
+      <c r="A750" s="15"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="13"/>
+      <c r="A751" s="15"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="13"/>
+      <c r="A752" s="15"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="13"/>
+      <c r="A753" s="15"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="13"/>
+      <c r="A754" s="15"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="13"/>
+      <c r="A755" s="15"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="13"/>
+      <c r="A756" s="15"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="13"/>
+      <c r="A757" s="15"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="13"/>
+      <c r="A758" s="15"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="13"/>
+      <c r="A759" s="15"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="13"/>
+      <c r="A760" s="15"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="13"/>
+      <c r="A761" s="15"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="13"/>
+      <c r="A762" s="15"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="13"/>
+      <c r="A763" s="15"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="13"/>
+      <c r="A764" s="15"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="13"/>
+      <c r="A765" s="15"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="13"/>
+      <c r="A766" s="15"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="13"/>
+      <c r="A767" s="15"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="13"/>
+      <c r="A768" s="15"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="13"/>
+      <c r="A769" s="15"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="13"/>
+      <c r="A770" s="15"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="13"/>
+      <c r="A771" s="15"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="13"/>
+      <c r="A772" s="15"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="13"/>
+      <c r="A773" s="15"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="13"/>
+      <c r="A774" s="15"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="13"/>
+      <c r="A775" s="15"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="13"/>
+      <c r="A776" s="15"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="13"/>
+      <c r="A777" s="15"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="13"/>
+      <c r="A778" s="15"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="13"/>
+      <c r="A779" s="15"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="13"/>
+      <c r="A780" s="15"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="13"/>
+      <c r="A781" s="15"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="13"/>
+      <c r="A782" s="15"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="13"/>
+      <c r="A783" s="15"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="13"/>
+      <c r="A784" s="15"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="13"/>
+      <c r="A785" s="15"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="13"/>
+      <c r="A786" s="15"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="13"/>
+      <c r="A787" s="15"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="13"/>
+      <c r="A788" s="15"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="13"/>
+      <c r="A789" s="15"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="13"/>
+      <c r="A790" s="15"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="13"/>
+      <c r="A791" s="15"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="13"/>
+      <c r="A792" s="15"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="13"/>
+      <c r="A793" s="15"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="13"/>
+      <c r="A794" s="15"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="13"/>
+      <c r="A795" s="15"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="13"/>
+      <c r="A796" s="15"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="13"/>
+      <c r="A797" s="15"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="13"/>
+      <c r="A798" s="15"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="13"/>
+      <c r="A799" s="15"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="13"/>
+      <c r="A800" s="15"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="13"/>
+      <c r="A801" s="15"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="13"/>
+      <c r="A802" s="15"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="13"/>
+      <c r="A803" s="15"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="13"/>
+      <c r="A804" s="15"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="13"/>
+      <c r="A805" s="15"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="13"/>
+      <c r="A806" s="15"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="13"/>
+      <c r="A807" s="15"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="13"/>
+      <c r="A808" s="15"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="13"/>
+      <c r="A809" s="15"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="13"/>
+      <c r="A810" s="15"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="13"/>
+      <c r="A811" s="15"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="13"/>
+      <c r="A812" s="15"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="13"/>
+      <c r="A813" s="15"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="13"/>
+      <c r="A814" s="15"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="13"/>
+      <c r="A815" s="15"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="13"/>
+      <c r="A816" s="15"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="13"/>
+      <c r="A817" s="15"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="13"/>
+      <c r="A818" s="15"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="13"/>
+      <c r="A819" s="15"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="13"/>
+      <c r="A820" s="15"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="13"/>
+      <c r="A821" s="15"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="13"/>
+      <c r="A822" s="15"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="13"/>
+      <c r="A823" s="15"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="13"/>
+      <c r="A824" s="15"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="13"/>
+      <c r="A825" s="15"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="13"/>
+      <c r="A826" s="15"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="13"/>
+      <c r="A827" s="15"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="13"/>
+      <c r="A828" s="15"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="13"/>
+      <c r="A829" s="15"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="13"/>
+      <c r="A830" s="15"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="13"/>
+      <c r="A831" s="15"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="13"/>
+      <c r="A832" s="15"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="13"/>
+      <c r="A833" s="15"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="13"/>
+      <c r="A834" s="15"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="13"/>
+      <c r="A835" s="15"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="13"/>
+      <c r="A836" s="15"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="13"/>
+      <c r="A837" s="15"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="13"/>
+      <c r="A838" s="15"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="13"/>
+      <c r="A839" s="15"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="13"/>
+      <c r="A840" s="15"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="13"/>
+      <c r="A841" s="15"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="13"/>
+      <c r="A842" s="15"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="13"/>
+      <c r="A843" s="15"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="13"/>
+      <c r="A844" s="15"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="13"/>
+      <c r="A845" s="15"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="13"/>
+      <c r="A846" s="15"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="13"/>
+      <c r="A847" s="15"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="13"/>
+      <c r="A848" s="15"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="13"/>
+      <c r="A849" s="15"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="13"/>
+      <c r="A850" s="15"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="13"/>
+      <c r="A851" s="15"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="13"/>
+      <c r="A852" s="15"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="13"/>
+      <c r="A853" s="15"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="13"/>
+      <c r="A854" s="15"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="13"/>
+      <c r="A855" s="15"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="13"/>
+      <c r="A856" s="15"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="13"/>
+      <c r="A857" s="15"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="13"/>
+      <c r="A858" s="15"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="13"/>
+      <c r="A859" s="15"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="13"/>
+      <c r="A860" s="15"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="13"/>
+      <c r="A861" s="15"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="13"/>
+      <c r="A862" s="15"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="13"/>
+      <c r="A863" s="15"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="13"/>
+      <c r="A864" s="15"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="13"/>
+      <c r="A865" s="15"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="13"/>
+      <c r="A866" s="15"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="13"/>
+      <c r="A867" s="15"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="13"/>
+      <c r="A868" s="15"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="13"/>
+      <c r="A869" s="15"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="13"/>
+      <c r="A870" s="15"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="13"/>
+      <c r="A871" s="15"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="13"/>
+      <c r="A872" s="15"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="13"/>
+      <c r="A873" s="15"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="13"/>
+      <c r="A874" s="15"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="13"/>
+      <c r="A875" s="15"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="13"/>
+      <c r="A876" s="15"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="13"/>
+      <c r="A877" s="15"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="13"/>
+      <c r="A878" s="15"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="13"/>
+      <c r="A879" s="15"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="13"/>
+      <c r="A880" s="15"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="13"/>
+      <c r="A881" s="15"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="13"/>
+      <c r="A882" s="15"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="13"/>
+      <c r="A883" s="15"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="13"/>
+      <c r="A884" s="15"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="13"/>
+      <c r="A885" s="15"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="13"/>
+      <c r="A886" s="15"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="13"/>
+      <c r="A887" s="15"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="13"/>
+      <c r="A888" s="15"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="13"/>
+      <c r="A889" s="15"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="13"/>
+      <c r="A890" s="15"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="13"/>
+      <c r="A891" s="15"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="13"/>
+      <c r="A892" s="15"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="13"/>
+      <c r="A893" s="15"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="13"/>
+      <c r="A894" s="15"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="13"/>
+      <c r="A895" s="15"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="13"/>
+      <c r="A896" s="15"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="13"/>
+      <c r="A897" s="15"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="13"/>
+      <c r="A898" s="15"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="13"/>
+      <c r="A899" s="15"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="13"/>
+      <c r="A900" s="15"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="13"/>
+      <c r="A901" s="15"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="13"/>
+      <c r="A902" s="15"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="13"/>
+      <c r="A903" s="15"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="13"/>
+      <c r="A904" s="15"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="13"/>
+      <c r="A905" s="15"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="13"/>
+      <c r="A906" s="15"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="13"/>
+      <c r="A907" s="15"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="13"/>
+      <c r="A908" s="15"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="13"/>
+      <c r="A909" s="15"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="13"/>
+      <c r="A910" s="15"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="13"/>
+      <c r="A911" s="15"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="13"/>
+      <c r="A912" s="15"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="13"/>
+      <c r="A913" s="15"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="13"/>
+      <c r="A914" s="15"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="13"/>
+      <c r="A915" s="15"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="13"/>
+      <c r="A916" s="15"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="13"/>
+      <c r="A917" s="15"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="13"/>
+      <c r="A918" s="15"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="13"/>
+      <c r="A919" s="15"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="13"/>
+      <c r="A920" s="15"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="13"/>
+      <c r="A921" s="15"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="13"/>
+      <c r="A922" s="15"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="13"/>
+      <c r="A923" s="15"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="13"/>
+      <c r="A924" s="15"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="13"/>
+      <c r="A925" s="15"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="13"/>
+      <c r="A926" s="15"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="13"/>
+      <c r="A927" s="15"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="13"/>
+      <c r="A928" s="15"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="13"/>
+      <c r="A929" s="15"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="13"/>
+      <c r="A930" s="15"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="13"/>
+      <c r="A931" s="15"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="13"/>
+      <c r="A932" s="15"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="13"/>
+      <c r="A933" s="15"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="13"/>
+      <c r="A934" s="15"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="13"/>
+      <c r="A935" s="15"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="13"/>
+      <c r="A936" s="15"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="13"/>
+      <c r="A937" s="15"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="13"/>
+      <c r="A938" s="15"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="13"/>
+      <c r="A939" s="15"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="13"/>
+      <c r="A940" s="15"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="13"/>
+      <c r="A941" s="15"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="13"/>
+      <c r="A942" s="15"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="13"/>
+      <c r="A943" s="15"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="13"/>
+      <c r="A944" s="15"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="13"/>
+      <c r="A945" s="15"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="13"/>
+      <c r="A946" s="15"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="13"/>
+      <c r="A947" s="15"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="13"/>
+      <c r="A948" s="15"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="13"/>
+      <c r="A949" s="15"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="13"/>
+      <c r="A950" s="15"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="13"/>
+      <c r="A951" s="15"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="13"/>
+      <c r="A952" s="15"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="13"/>
+      <c r="A953" s="15"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="13"/>
+      <c r="A954" s="15"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="13"/>
+      <c r="A955" s="15"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="13"/>
+      <c r="A956" s="15"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="13"/>
+      <c r="A957" s="15"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="13"/>
+      <c r="A958" s="15"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="13"/>
+      <c r="A959" s="15"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="13"/>
+      <c r="A960" s="15"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="13"/>
+      <c r="A961" s="15"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="13"/>
+      <c r="A962" s="15"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="13"/>
+      <c r="A963" s="15"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="13"/>
+      <c r="A964" s="15"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="13"/>
+      <c r="A965" s="15"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="13"/>
+      <c r="A966" s="15"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="13"/>
+      <c r="A967" s="15"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="13"/>
+      <c r="A968" s="15"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="13"/>
+      <c r="A969" s="15"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="13"/>
+      <c r="A970" s="15"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="13"/>
+      <c r="A971" s="15"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="13"/>
+      <c r="A972" s="15"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="13"/>
+      <c r="A973" s="15"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="13"/>
+      <c r="A974" s="15"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="13"/>
+      <c r="A975" s="15"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="13"/>
+      <c r="A976" s="15"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="13"/>
+      <c r="A977" s="15"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="13"/>
+      <c r="A978" s="15"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="13"/>
+      <c r="A979" s="15"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="13"/>
+      <c r="A980" s="15"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="13"/>
+      <c r="A981" s="15"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="13"/>
+      <c r="A982" s="15"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="13"/>
+      <c r="A983" s="15"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="13"/>
+      <c r="A984" s="15"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="13"/>
+      <c r="A985" s="15"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="13"/>
+      <c r="A986" s="15"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="13"/>
+      <c r="A987" s="15"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="13"/>
+      <c r="A988" s="15"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="13"/>
+      <c r="A989" s="15"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="13"/>
+      <c r="A990" s="15"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="13"/>
+      <c r="A991" s="15"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="13"/>
+      <c r="A992" s="15"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="13"/>
+      <c r="A993" s="15"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="13"/>
+      <c r="A994" s="15"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="13"/>
+      <c r="A995" s="15"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="13"/>
+      <c r="A996" s="15"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="13"/>
+      <c r="A997" s="15"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="13"/>
+      <c r="A998" s="15"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="13"/>
+      <c r="A999" s="15"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="13"/>
+      <c r="A1000" s="15"/>
+    </row>
+    <row r="1001" ht="15.75" customHeight="1">
+      <c r="A1001" s="15"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C14"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -33753,54 +33752,110 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="s">
-        <v>179</v>
+      <c r="A1" s="18" t="s">
+        <v>187</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>180</v>
+      <c r="B1" s="18" t="s">
+        <v>188</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>181</v>
+      <c r="C1" s="18" t="s">
+        <v>189</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>182</v>
+      <c r="D1" s="18" t="s">
+        <v>190</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>183</v>
+      <c r="E1" s="19" t="s">
+        <v>191</v>
       </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
     </row>
     <row r="2">
-      <c r="A2" s="15">
+      <c r="A2" s="21">
         <v>1.0</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>184</v>
+      <c r="B2" s="18" t="s">
+        <v>192</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>185</v>
+      <c r="C2" s="22"/>
+      <c r="D2" s="18" t="s">
+        <v>193</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>186</v>
+      <c r="E2" s="23" t="s">
+        <v>194</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>187</v>
+    </row>
+    <row r="3">
+      <c r="A3" s="21">
+        <v>2.0</v>
       </c>
+      <c r="B3" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="21.29"/>
-  </cols>
-  <sheetData/>
+  <mergeCells count="3">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E5:F5"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>